--- a/undervisningsforlob/kandidattest/Datasæt_16_personer.xlsx
+++ b/undervisningsforlob/kandidattest/Datasæt_16_personer.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aalbcitygym-my.sharepoint.com/personal/js_aacg_dk/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AI\aalborg-intelligence.github.io\undervisningsforlob\kandidattest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="8_{A5BEE592-78B9-43C0-89E1-CEBBFB5E478F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{890D470F-C234-4990-8D52-6A5979BD32E3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F42EF16E-43D8-4FBC-8E04-91E2BDD7015C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{511EBD6E-ABDC-4801-9D1A-BF7062899228}"/>
   </bookViews>
